--- a/output/06_Ceragon_구성방식별_BoM_정리.xlsx
+++ b/output/06_Ceragon_구성방식별_BoM_정리.xlsx
@@ -478,14 +478,14 @@
   <dimension ref="A1:H494"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
     <col width="56" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -18100,7 +18100,7 @@
     <row r="476">
       <c r="A476" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R484</t>
+          <t>K9212896</t>
         </is>
       </c>
       <c r="B476" s="2" t="inlineStr">
@@ -18123,16 +18123,16 @@
         <v>7527169</v>
       </c>
       <c r="G476" s="4" t="n"/>
-      <c r="H476" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R485</t>
+          <t>K9213016</t>
         </is>
       </c>
       <c r="B477" s="2" t="inlineStr">
@@ -18155,16 +18155,16 @@
         <v>2840000</v>
       </c>
       <c r="G477" s="4" t="n"/>
-      <c r="H477" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R486</t>
+          <t>K9213017</t>
         </is>
       </c>
       <c r="B478" s="2" t="inlineStr">
@@ -18187,16 +18187,16 @@
         <v>4958142</v>
       </c>
       <c r="G478" s="4" t="n"/>
-      <c r="H478" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R487</t>
+          <t>K9213018</t>
         </is>
       </c>
       <c r="B479" s="2" t="inlineStr">
@@ -18219,16 +18219,16 @@
         <v>3141244</v>
       </c>
       <c r="G479" s="4" t="n"/>
-      <c r="H479" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R488</t>
+          <t>K9213019</t>
         </is>
       </c>
       <c r="B480" s="2" t="inlineStr">
@@ -18251,16 +18251,16 @@
         <v>2071000</v>
       </c>
       <c r="G480" s="4" t="n"/>
-      <c r="H480" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R489</t>
+          <t>K9213020</t>
         </is>
       </c>
       <c r="B481" s="2" t="inlineStr">
@@ -18283,16 +18283,16 @@
         <v>2010086</v>
       </c>
       <c r="G481" s="4" t="n"/>
-      <c r="H481" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H481" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R490</t>
+          <t>K9213021</t>
         </is>
       </c>
       <c r="B482" s="2" t="inlineStr">
@@ -18315,16 +18315,16 @@
         <v>202090</v>
       </c>
       <c r="G482" s="4" t="n"/>
-      <c r="H482" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H482" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R491</t>
+          <t>K9213022</t>
         </is>
       </c>
       <c r="B483" s="2" t="inlineStr">
@@ -18347,16 +18347,16 @@
         <v>296000</v>
       </c>
       <c r="G483" s="4" t="n"/>
-      <c r="H483" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H483" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R492</t>
+          <t>K9213023</t>
         </is>
       </c>
       <c r="B484" s="2" t="inlineStr">
@@ -18379,16 +18379,16 @@
         <v>7127400.777999999</v>
       </c>
       <c r="G484" s="4" t="n"/>
-      <c r="H484" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H484" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R493</t>
+          <t>K9213024</t>
         </is>
       </c>
       <c r="B485" s="2" t="inlineStr">
@@ -18411,16 +18411,16 @@
         <v>4365576.753</v>
       </c>
       <c r="G485" s="4" t="n"/>
-      <c r="H485" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H485" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R494</t>
+          <t>K9213025</t>
         </is>
       </c>
       <c r="B486" s="2" t="inlineStr">
@@ -18443,16 +18443,16 @@
         <v>4626985.309</v>
       </c>
       <c r="G486" s="4" t="n"/>
-      <c r="H486" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H486" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R495</t>
+          <t>K9213026</t>
         </is>
       </c>
       <c r="B487" s="2" t="inlineStr">
@@ -18475,16 +18475,16 @@
         <v>3377681.166</v>
       </c>
       <c r="G487" s="4" t="n"/>
-      <c r="H487" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H487" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R496</t>
+          <t>K9213027</t>
         </is>
       </c>
       <c r="B488" s="2" t="inlineStr">
@@ -18507,16 +18507,16 @@
         <v>1738258</v>
       </c>
       <c r="G488" s="4" t="n"/>
-      <c r="H488" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H488" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R497</t>
+          <t>K9213028</t>
         </is>
       </c>
       <c r="B489" s="2" t="inlineStr">
@@ -18539,16 +18539,16 @@
         <v>2330232</v>
       </c>
       <c r="G489" s="4" t="n"/>
-      <c r="H489" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H489" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R498</t>
+          <t>K9213029</t>
         </is>
       </c>
       <c r="B490" s="2" t="inlineStr">
@@ -18571,16 +18571,16 @@
         <v>311062</v>
       </c>
       <c r="G490" s="4" t="n"/>
-      <c r="H490" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H490" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R499</t>
+          <t>K9213030</t>
         </is>
       </c>
       <c r="B491" s="2" t="inlineStr">
@@ -18603,16 +18603,16 @@
         <v>858000</v>
       </c>
       <c r="G491" s="4" t="n"/>
-      <c r="H491" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H491" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R500</t>
+          <t>K9213031</t>
         </is>
       </c>
       <c r="B492" s="2" t="inlineStr">
@@ -18635,16 +18635,16 @@
         <v>8970000</v>
       </c>
       <c r="G492" s="4" t="n"/>
-      <c r="H492" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H492" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R501</t>
+          <t>K9213032</t>
         </is>
       </c>
       <c r="B493" s="2" t="inlineStr">
@@ -18667,16 +18667,16 @@
         <v>294000</v>
       </c>
       <c r="G493" s="4" t="n"/>
-      <c r="H493" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H493" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R502</t>
+          <t>K9213033</t>
         </is>
       </c>
       <c r="B494" s="2" t="inlineStr">
@@ -18699,9 +18699,9 @@
         <v>294000</v>
       </c>
       <c r="G494" s="4" t="n"/>
-      <c r="H494" s="5" t="inlineStr">
-        <is>
-          <t>신규코드(코드 미부여)</t>
+      <c r="H494" s="2" t="inlineStr">
+        <is>
+          <t>확인필요</t>
         </is>
       </c>
     </row>
@@ -18726,11 +18726,11 @@
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
     <col width="29" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
     <col width="53" customWidth="1" min="8" max="8"/>
     <col width="60" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
@@ -20191,7 +20191,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R493</t>
+          <t>K9213024</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -20211,7 +20211,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L19" s="3" t="n">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R492</t>
+          <t>K9213023</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -21847,7 +21847,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L40" s="3" t="n">
@@ -23853,7 +23853,7 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R495</t>
+          <t>K9213026</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -23873,7 +23873,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L66" s="3" t="n">
@@ -25879,7 +25879,7 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R494</t>
+          <t>K9213025</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
@@ -25899,7 +25899,7 @@
       </c>
       <c r="K92" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L92" s="3" t="n">
@@ -27671,7 +27671,7 @@
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R497</t>
+          <t>K9213028</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
@@ -27691,7 +27691,7 @@
       </c>
       <c r="K115" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L115" s="3" t="n">
@@ -29775,7 +29775,7 @@
       </c>
       <c r="G142" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R496</t>
+          <t>K9213027</t>
         </is>
       </c>
       <c r="H142" s="2" t="inlineStr">
@@ -29795,7 +29795,7 @@
       </c>
       <c r="K142" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L142" s="3" t="n">
@@ -31567,7 +31567,7 @@
       </c>
       <c r="G165" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R499</t>
+          <t>K9213030</t>
         </is>
       </c>
       <c r="H165" s="2" t="inlineStr">
@@ -31587,7 +31587,7 @@
       </c>
       <c r="K165" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L165" s="3" t="n">
@@ -33671,7 +33671,7 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R498</t>
+          <t>K9213029</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
@@ -33691,7 +33691,7 @@
       </c>
       <c r="K192" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L192" s="3" t="n">
@@ -35073,7 +35073,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R493</t>
+          <t>K9213024</t>
         </is>
       </c>
       <c r="H210" s="2" t="inlineStr">
@@ -35093,7 +35093,7 @@
       </c>
       <c r="K210" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L210" s="3" t="n">
@@ -36709,7 +36709,7 @@
       </c>
       <c r="G231" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R492</t>
+          <t>K9213023</t>
         </is>
       </c>
       <c r="H231" s="2" t="inlineStr">
@@ -36729,7 +36729,7 @@
       </c>
       <c r="K231" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L231" s="3" t="n">
@@ -38735,7 +38735,7 @@
       </c>
       <c r="G257" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R495</t>
+          <t>K9213026</t>
         </is>
       </c>
       <c r="H257" s="2" t="inlineStr">
@@ -38755,7 +38755,7 @@
       </c>
       <c r="K257" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L257" s="3" t="n">
@@ -40761,7 +40761,7 @@
       </c>
       <c r="G283" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R494</t>
+          <t>K9213025</t>
         </is>
       </c>
       <c r="H283" s="2" t="inlineStr">
@@ -40781,7 +40781,7 @@
       </c>
       <c r="K283" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L283" s="3" t="n">
@@ -42553,7 +42553,7 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R497</t>
+          <t>K9213028</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
@@ -42573,7 +42573,7 @@
       </c>
       <c r="K306" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L306" s="3" t="n">
@@ -44657,7 +44657,7 @@
       </c>
       <c r="G333" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R496</t>
+          <t>K9213027</t>
         </is>
       </c>
       <c r="H333" s="2" t="inlineStr">
@@ -44677,7 +44677,7 @@
       </c>
       <c r="K333" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L333" s="3" t="n">
@@ -46449,7 +46449,7 @@
       </c>
       <c r="G356" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R499</t>
+          <t>K9213030</t>
         </is>
       </c>
       <c r="H356" s="2" t="inlineStr">
@@ -46469,7 +46469,7 @@
       </c>
       <c r="K356" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L356" s="3" t="n">
@@ -48553,7 +48553,7 @@
       </c>
       <c r="G383" s="2" t="inlineStr">
         <is>
-          <t>신규코드-R498</t>
+          <t>K9213029</t>
         </is>
       </c>
       <c r="H383" s="2" t="inlineStr">
@@ -48573,7 +48573,7 @@
       </c>
       <c r="K383" s="2" t="inlineStr">
         <is>
-          <t>신규코드(코드 미부여)</t>
+          <t>확인필요</t>
         </is>
       </c>
       <c r="L383" s="3" t="n">

--- a/output/06_Ceragon_구성방식별_BoM_정리.xlsx
+++ b/output/06_Ceragon_구성방식별_BoM_정리.xlsx
@@ -1887,7 +1887,7 @@
         <v>207020</v>
       </c>
       <c r="F38" s="3" t="n">
-        <v>204872</v>
+        <v>202880</v>
       </c>
       <c r="G38" s="4">
         <f>1-F38/E38</f>
@@ -3996,7 +3996,7 @@
         <v>3494770</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>3424874.6</v>
+        <v>3389927</v>
       </c>
       <c r="G95" s="4">
         <f>1-F95/E95</f>
@@ -4033,7 +4033,7 @@
         <v>3494770</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>3424874.6</v>
+        <v>3389927</v>
       </c>
       <c r="G96" s="4">
         <f>1-F96/E96</f>
@@ -4070,7 +4070,7 @@
         <v>3494770</v>
       </c>
       <c r="F97" s="3" t="n">
-        <v>3424874.6</v>
+        <v>3389927</v>
       </c>
       <c r="G97" s="4">
         <f>1-F97/E97</f>
@@ -4107,7 +4107,7 @@
         <v>3494770</v>
       </c>
       <c r="F98" s="3" t="n">
-        <v>3424874.6</v>
+        <v>3389927</v>
       </c>
       <c r="G98" s="4">
         <f>1-F98/E98</f>
@@ -4144,7 +4144,7 @@
         <v>4919190</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>4820806.2</v>
+        <v>4771614</v>
       </c>
       <c r="G99" s="4">
         <f>1-F99/E99</f>
@@ -4181,7 +4181,7 @@
         <v>4919190</v>
       </c>
       <c r="F100" s="3" t="n">
-        <v>4820806.2</v>
+        <v>4771614</v>
       </c>
       <c r="G100" s="4">
         <f>1-F100/E100</f>
@@ -4218,7 +4218,7 @@
         <v>4919190</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>4820806.2</v>
+        <v>4771614</v>
       </c>
       <c r="G101" s="4">
         <f>1-F101/E101</f>
@@ -4255,7 +4255,7 @@
         <v>4919190</v>
       </c>
       <c r="F102" s="3" t="n">
-        <v>4820806.2</v>
+        <v>4771614</v>
       </c>
       <c r="G102" s="4">
         <f>1-F102/E102</f>
@@ -4292,7 +4292,7 @@
         <v>6542350</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>6411503</v>
+        <v>6346080</v>
       </c>
       <c r="G103" s="4">
         <f>1-F103/E103</f>
@@ -4329,7 +4329,7 @@
         <v>6542350</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>6411503</v>
+        <v>6346080</v>
       </c>
       <c r="G104" s="4">
         <f>1-F104/E104</f>
@@ -4366,7 +4366,7 @@
         <v>6542350</v>
       </c>
       <c r="F105" s="3" t="n">
-        <v>6411503</v>
+        <v>6346080</v>
       </c>
       <c r="G105" s="4">
         <f>1-F105/E105</f>
@@ -4403,7 +4403,7 @@
         <v>6542350</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>6411503</v>
+        <v>6346080</v>
       </c>
       <c r="G106" s="4">
         <f>1-F106/E106</f>
@@ -4440,7 +4440,7 @@
         <v>8631560</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>8458928.800000001</v>
+        <v>8372613</v>
       </c>
       <c r="G107" s="4">
         <f>1-F107/E107</f>
@@ -4477,7 +4477,7 @@
         <v>8631560</v>
       </c>
       <c r="F108" s="3" t="n">
-        <v>8458928.800000001</v>
+        <v>8372613</v>
       </c>
       <c r="G108" s="4">
         <f>1-F108/E108</f>
@@ -4514,7 +4514,7 @@
         <v>8631560</v>
       </c>
       <c r="F109" s="3" t="n">
-        <v>8458928.800000001</v>
+        <v>8372613</v>
       </c>
       <c r="G109" s="4">
         <f>1-F109/E109</f>
@@ -4551,7 +4551,7 @@
         <v>8631560</v>
       </c>
       <c r="F110" s="3" t="n">
-        <v>8458928.800000001</v>
+        <v>8372613</v>
       </c>
       <c r="G110" s="4">
         <f>1-F110/E110</f>
@@ -4588,7 +4588,7 @@
         <v>10927020</v>
       </c>
       <c r="F111" s="3" t="n">
-        <v>10708479.6</v>
+        <v>10599209</v>
       </c>
       <c r="G111" s="4">
         <f>1-F111/E111</f>
@@ -4625,7 +4625,7 @@
         <v>10927020</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>10708479.6</v>
+        <v>10599209</v>
       </c>
       <c r="G112" s="4">
         <f>1-F112/E112</f>
@@ -4662,7 +4662,7 @@
         <v>10927020</v>
       </c>
       <c r="F113" s="3" t="n">
-        <v>10708479.6</v>
+        <v>10599209</v>
       </c>
       <c r="G113" s="4">
         <f>1-F113/E113</f>
@@ -4699,7 +4699,7 @@
         <v>10927020</v>
       </c>
       <c r="F114" s="3" t="n">
-        <v>10708479.6</v>
+        <v>10599209</v>
       </c>
       <c r="G114" s="4">
         <f>1-F114/E114</f>
@@ -4736,7 +4736,7 @@
         <v>14163130</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>13879867.4</v>
+        <v>13738236</v>
       </c>
       <c r="G115" s="4">
         <f>1-F115/E115</f>
@@ -4773,7 +4773,7 @@
         <v>14163130</v>
       </c>
       <c r="F116" s="3" t="n">
-        <v>13879867.4</v>
+        <v>13738236</v>
       </c>
       <c r="G116" s="4">
         <f>1-F116/E116</f>
@@ -4810,7 +4810,7 @@
         <v>14163130</v>
       </c>
       <c r="F117" s="3" t="n">
-        <v>13879867.4</v>
+        <v>13738236</v>
       </c>
       <c r="G117" s="4">
         <f>1-F117/E117</f>
@@ -4847,7 +4847,7 @@
         <v>14163130</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>13879867.4</v>
+        <v>13738236</v>
       </c>
       <c r="G118" s="4">
         <f>1-F118/E118</f>
@@ -4995,7 +4995,7 @@
         <v>5343190</v>
       </c>
       <c r="F122" s="3" t="n">
-        <v>5236326.2</v>
+        <v>5182894</v>
       </c>
       <c r="G122" s="4">
         <f>1-F122/E122</f>
@@ -5032,7 +5032,7 @@
         <v>5343190</v>
       </c>
       <c r="F123" s="3" t="n">
-        <v>5236326.2</v>
+        <v>5182894</v>
       </c>
       <c r="G123" s="4">
         <f>1-F123/E123</f>
@@ -5069,7 +5069,7 @@
         <v>5343190</v>
       </c>
       <c r="F124" s="3" t="n">
-        <v>5236326.2</v>
+        <v>5182894</v>
       </c>
       <c r="G124" s="4">
         <f>1-F124/E124</f>
@@ -5846,7 +5846,7 @@
         <v>548550</v>
       </c>
       <c r="F145" s="3" t="n">
-        <v>634418</v>
+        <v>467968</v>
       </c>
       <c r="G145" s="4">
         <f>1-F145/E145</f>
@@ -5920,7 +5920,7 @@
         <v>123210</v>
       </c>
       <c r="F147" s="3" t="n">
-        <v>634418</v>
+        <v>105110</v>
       </c>
       <c r="G147" s="4">
         <f>1-F147/E147</f>
@@ -6623,7 +6623,7 @@
         <v>3024380</v>
       </c>
       <c r="F166" s="3" t="n">
-        <v>2963892.4</v>
+        <v>2933649</v>
       </c>
       <c r="G166" s="4">
         <f>1-F166/E166</f>
@@ -6660,7 +6660,7 @@
         <v>3024380</v>
       </c>
       <c r="F167" s="3" t="n">
-        <v>2963892.4</v>
+        <v>2933649</v>
       </c>
       <c r="G167" s="4">
         <f>1-F167/E167</f>
@@ -6697,7 +6697,7 @@
         <v>3024380</v>
       </c>
       <c r="F168" s="3" t="n">
-        <v>2963892.4</v>
+        <v>2933649</v>
       </c>
       <c r="G168" s="4">
         <f>1-F168/E168</f>
@@ -6734,7 +6734,7 @@
         <v>5343190</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>5236326.2</v>
+        <v>5182894</v>
       </c>
       <c r="G169" s="4">
         <f>1-F169/E169</f>
@@ -11655,7 +11655,7 @@
         <v>11774430</v>
       </c>
       <c r="F302" s="3" t="n">
-        <v>11538941.4</v>
+        <v>11421197</v>
       </c>
       <c r="G302" s="4">
         <f>1-F302/E302</f>
@@ -15865,7 +15865,7 @@
         <v>26220</v>
       </c>
       <c r="F415" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="G415" s="4">
         <f>1-F415/E415</f>
@@ -15939,7 +15939,7 @@
         <v>43070</v>
       </c>
       <c r="F417" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="G417" s="4">
         <f>1-F417/E417</f>
@@ -16050,7 +16050,7 @@
         <v>46820</v>
       </c>
       <c r="F420" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="G420" s="4">
         <f>1-F420/E420</f>
@@ -16864,7 +16864,7 @@
         <v>7187030</v>
       </c>
       <c r="F442" s="3" t="n">
-        <v>7043289.4</v>
+        <v>6971419</v>
       </c>
       <c r="G442" s="4">
         <f>1-F442/E442</f>
@@ -16901,7 +16901,7 @@
         <v>8738110</v>
       </c>
       <c r="F443" s="3" t="n">
-        <v>8563347.800000001</v>
+        <v>8475967</v>
       </c>
       <c r="G443" s="4">
         <f>1-F443/E443</f>
@@ -16938,7 +16938,7 @@
         <v>13804820</v>
       </c>
       <c r="F444" s="3" t="n">
-        <v>13528723.6</v>
+        <v>13390675</v>
       </c>
       <c r="G444" s="4">
         <f>1-F444/E444</f>
@@ -16975,7 +16975,7 @@
         <v>17633830</v>
       </c>
       <c r="F445" s="3" t="n">
-        <v>17281153.4</v>
+        <v>17104815</v>
       </c>
       <c r="G445" s="4">
         <f>1-F445/E445</f>
@@ -18901,13 +18901,13 @@
         <v>26220</v>
       </c>
       <c r="P2" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q2" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="3">
@@ -19291,13 +19291,13 @@
         <v>46820</v>
       </c>
       <c r="P7" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q7" s="3" t="n">
         <v>187280</v>
       </c>
       <c r="R7" s="3" t="n">
-        <v>185407.2</v>
+        <v>177916</v>
       </c>
     </row>
     <row r="8">
@@ -20459,13 +20459,13 @@
         <v>26220</v>
       </c>
       <c r="P22" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q22" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R22" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="23">
@@ -20537,13 +20537,13 @@
         <v>46820</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>374560</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>370814.4</v>
+        <v>355832</v>
       </c>
     </row>
     <row r="24">
@@ -20927,13 +20927,13 @@
         <v>43070</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="Q28" s="3" t="n">
         <v>172280</v>
       </c>
       <c r="R28" s="3" t="n">
-        <v>170557.2</v>
+        <v>163664</v>
       </c>
     </row>
     <row r="29">
@@ -22251,13 +22251,13 @@
         <v>26220</v>
       </c>
       <c r="P45" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q45" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R45" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="46">
@@ -22329,13 +22329,13 @@
         <v>46820</v>
       </c>
       <c r="P46" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q46" s="3" t="n">
         <v>374560</v>
       </c>
       <c r="R46" s="3" t="n">
-        <v>370814.4</v>
+        <v>355832</v>
       </c>
     </row>
     <row r="47">
@@ -23965,13 +23965,13 @@
         <v>46820</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q67" s="3" t="n">
         <v>749120</v>
       </c>
       <c r="R67" s="3" t="n">
-        <v>741628.8</v>
+        <v>711664</v>
       </c>
     </row>
     <row r="68">
@@ -24433,13 +24433,13 @@
         <v>26220</v>
       </c>
       <c r="P73" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q73" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R73" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="74">
@@ -24511,13 +24511,13 @@
         <v>43070</v>
       </c>
       <c r="P74" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="Q74" s="3" t="n">
         <v>344560</v>
       </c>
       <c r="R74" s="3" t="n">
-        <v>341114.4</v>
+        <v>327328</v>
       </c>
     </row>
     <row r="75">
@@ -25991,13 +25991,13 @@
         <v>46820</v>
       </c>
       <c r="P93" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q93" s="3" t="n">
         <v>561840</v>
       </c>
       <c r="R93" s="3" t="n">
-        <v>556221.6000000001</v>
+        <v>533748</v>
       </c>
     </row>
     <row r="94">
@@ -26069,13 +26069,13 @@
         <v>26220</v>
       </c>
       <c r="P94" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q94" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R94" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="95">
@@ -27783,13 +27783,13 @@
         <v>46820</v>
       </c>
       <c r="P116" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q116" s="3" t="n">
         <v>1123680</v>
       </c>
       <c r="R116" s="3" t="n">
-        <v>1112443.2</v>
+        <v>1067496</v>
       </c>
     </row>
     <row r="117">
@@ -28017,13 +28017,13 @@
         <v>43070</v>
       </c>
       <c r="P119" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="Q119" s="3" t="n">
         <v>516840</v>
       </c>
       <c r="R119" s="3" t="n">
-        <v>511671.6</v>
+        <v>490992</v>
       </c>
     </row>
     <row r="120">
@@ -28407,13 +28407,13 @@
         <v>26220</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q124" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R124" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="125">
@@ -29887,13 +29887,13 @@
         <v>46820</v>
       </c>
       <c r="P143" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q143" s="3" t="n">
         <v>749120</v>
       </c>
       <c r="R143" s="3" t="n">
-        <v>741628.8</v>
+        <v>711664</v>
       </c>
     </row>
     <row r="144">
@@ -30277,13 +30277,13 @@
         <v>26220</v>
       </c>
       <c r="P148" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q148" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R148" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="149">
@@ -31679,13 +31679,13 @@
         <v>46820</v>
       </c>
       <c r="P166" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q166" s="3" t="n">
         <v>1498240</v>
       </c>
       <c r="R166" s="3" t="n">
-        <v>1483257.6</v>
+        <v>1423328</v>
       </c>
     </row>
     <row r="167">
@@ -31991,13 +31991,13 @@
         <v>43070</v>
       </c>
       <c r="P170" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="Q170" s="3" t="n">
         <v>689120</v>
       </c>
       <c r="R170" s="3" t="n">
-        <v>682228.8</v>
+        <v>654656</v>
       </c>
     </row>
     <row r="171">
@@ -32537,13 +32537,13 @@
         <v>26220</v>
       </c>
       <c r="P177" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q177" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R177" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="178">
@@ -33783,13 +33783,13 @@
         <v>26220</v>
       </c>
       <c r="P193" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q193" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R193" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="194">
@@ -34173,13 +34173,13 @@
         <v>46820</v>
       </c>
       <c r="P198" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q198" s="3" t="n">
         <v>187280</v>
       </c>
       <c r="R198" s="3" t="n">
-        <v>185407.2</v>
+        <v>177916</v>
       </c>
     </row>
     <row r="199">
@@ -35341,13 +35341,13 @@
         <v>26220</v>
       </c>
       <c r="P213" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q213" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R213" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="214">
@@ -35419,13 +35419,13 @@
         <v>46820</v>
       </c>
       <c r="P214" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q214" s="3" t="n">
         <v>374560</v>
       </c>
       <c r="R214" s="3" t="n">
-        <v>370814.4</v>
+        <v>355832</v>
       </c>
     </row>
     <row r="215">
@@ -35809,13 +35809,13 @@
         <v>43070</v>
       </c>
       <c r="P219" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="Q219" s="3" t="n">
         <v>172280</v>
       </c>
       <c r="R219" s="3" t="n">
-        <v>170557.2</v>
+        <v>163664</v>
       </c>
     </row>
     <row r="220">
@@ -37133,13 +37133,13 @@
         <v>26220</v>
       </c>
       <c r="P236" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q236" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R236" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="237">
@@ -37211,13 +37211,13 @@
         <v>46820</v>
       </c>
       <c r="P237" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q237" s="3" t="n">
         <v>374560</v>
       </c>
       <c r="R237" s="3" t="n">
-        <v>370814.4</v>
+        <v>355832</v>
       </c>
     </row>
     <row r="238">
@@ -38847,13 +38847,13 @@
         <v>46820</v>
       </c>
       <c r="P258" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q258" s="3" t="n">
         <v>749120</v>
       </c>
       <c r="R258" s="3" t="n">
-        <v>741628.8</v>
+        <v>711664</v>
       </c>
     </row>
     <row r="259">
@@ -39315,13 +39315,13 @@
         <v>26220</v>
       </c>
       <c r="P264" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q264" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R264" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="265">
@@ -39393,13 +39393,13 @@
         <v>43070</v>
       </c>
       <c r="P265" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="Q265" s="3" t="n">
         <v>344560</v>
       </c>
       <c r="R265" s="3" t="n">
-        <v>341114.4</v>
+        <v>327328</v>
       </c>
     </row>
     <row r="266">
@@ -40873,13 +40873,13 @@
         <v>46820</v>
       </c>
       <c r="P284" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q284" s="3" t="n">
         <v>561840</v>
       </c>
       <c r="R284" s="3" t="n">
-        <v>556221.6000000001</v>
+        <v>533748</v>
       </c>
     </row>
     <row r="285">
@@ -40951,13 +40951,13 @@
         <v>26220</v>
       </c>
       <c r="P285" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q285" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R285" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="286">
@@ -42665,13 +42665,13 @@
         <v>46820</v>
       </c>
       <c r="P307" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q307" s="3" t="n">
         <v>1123680</v>
       </c>
       <c r="R307" s="3" t="n">
-        <v>1112443.2</v>
+        <v>1067496</v>
       </c>
     </row>
     <row r="308">
@@ -42899,13 +42899,13 @@
         <v>43070</v>
       </c>
       <c r="P310" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="Q310" s="3" t="n">
         <v>516840</v>
       </c>
       <c r="R310" s="3" t="n">
-        <v>511671.6</v>
+        <v>490992</v>
       </c>
     </row>
     <row r="311">
@@ -43289,13 +43289,13 @@
         <v>26220</v>
       </c>
       <c r="P315" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q315" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R315" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="316">
@@ -44769,13 +44769,13 @@
         <v>46820</v>
       </c>
       <c r="P334" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q334" s="3" t="n">
         <v>749120</v>
       </c>
       <c r="R334" s="3" t="n">
-        <v>741628.8</v>
+        <v>711664</v>
       </c>
     </row>
     <row r="335">
@@ -45159,13 +45159,13 @@
         <v>26220</v>
       </c>
       <c r="P339" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q339" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R339" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="340">
@@ -46561,13 +46561,13 @@
         <v>46820</v>
       </c>
       <c r="P357" s="3" t="n">
-        <v>46351.8</v>
+        <v>44479</v>
       </c>
       <c r="Q357" s="3" t="n">
         <v>1498240</v>
       </c>
       <c r="R357" s="3" t="n">
-        <v>1483257.6</v>
+        <v>1423328</v>
       </c>
     </row>
     <row r="358">
@@ -46873,13 +46873,13 @@
         <v>43070</v>
       </c>
       <c r="P361" s="3" t="n">
-        <v>42639.3</v>
+        <v>40916</v>
       </c>
       <c r="Q361" s="3" t="n">
         <v>689120</v>
       </c>
       <c r="R361" s="3" t="n">
-        <v>682228.8</v>
+        <v>654656</v>
       </c>
     </row>
     <row r="362">
@@ -47419,13 +47419,13 @@
         <v>26220</v>
       </c>
       <c r="P368" s="3" t="n">
-        <v>25957.8</v>
+        <v>24909</v>
       </c>
       <c r="Q368" s="3" t="n">
         <v>209760</v>
       </c>
       <c r="R368" s="3" t="n">
-        <v>207662.4</v>
+        <v>199272</v>
       </c>
     </row>
     <row r="369">
@@ -48695,7 +48695,7 @@
         <v>40476180</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="H2" s="3">
         <f>F2-G2</f>
@@ -48732,7 +48732,7 @@
         <v>56118320</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>47709791.64199999</v>
+        <v>47679525.64199999</v>
       </c>
       <c r="H3" s="3">
         <f>F3-G3</f>
@@ -48769,7 +48769,7 @@
         <v>74123280</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>55702281.60600001</v>
+        <v>55678908.80600001</v>
       </c>
       <c r="H4" s="3">
         <f>F4-G4</f>
@@ -48806,7 +48806,7 @@
         <v>101081020</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>65922530.36799998</v>
+        <v>65870388.76799998</v>
       </c>
       <c r="H5" s="3">
         <f>F5-G5</f>
@@ -48843,7 +48843,7 @@
         <v>110808660</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>75623633.18000001</v>
+        <v>75592769.18000001</v>
       </c>
       <c r="H6" s="3">
         <f>F6-G6</f>
@@ -48880,7 +48880,7 @@
         <v>149238640</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>83887705.41800003</v>
+        <v>83813688.21800002</v>
       </c>
       <c r="H7" s="3">
         <f>F7-G7</f>
@@ -48917,7 +48917,7 @@
         <v>140480020</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>91509301.57800001</v>
+        <v>91470946.37800001</v>
       </c>
       <c r="H8" s="3">
         <f>F8-G8</f>
@@ -48954,7 +48954,7 @@
         <v>193801700</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>103905950.198</v>
+        <v>103810057.398</v>
       </c>
       <c r="H9" s="3">
         <f>F9-G9</f>
@@ -48991,7 +48991,7 @@
         <v>40476180</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>35608005.346</v>
+        <v>35592123.746</v>
       </c>
       <c r="H10" s="3">
         <f>F10-G10</f>
@@ -49028,7 +49028,7 @@
         <v>55941700</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>47710885.87799999</v>
+        <v>47680619.87799999</v>
       </c>
       <c r="H11" s="3">
         <f>F11-G11</f>
@@ -49065,7 +49065,7 @@
         <v>73770040</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>55704470.07800001</v>
+        <v>55681097.27800001</v>
       </c>
       <c r="H12" s="3">
         <f>F12-G12</f>
@@ -49102,7 +49102,7 @@
         <v>100727780</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>65924718.83999998</v>
+        <v>65872577.23999999</v>
       </c>
       <c r="H13" s="3">
         <f>F13-G13</f>
@@ -49139,7 +49139,7 @@
         <v>110278800</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>75626915.888</v>
+        <v>75596051.888</v>
       </c>
       <c r="H14" s="3">
         <f>F14-G14</f>
@@ -49176,7 +49176,7 @@
         <v>148708780</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>83890988.12600002</v>
+        <v>83816970.92600001</v>
       </c>
       <c r="H15" s="3">
         <f>F15-G15</f>
@@ -49213,7 +49213,7 @@
         <v>139773540</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>91513678.52200001</v>
+        <v>91475323.32200001</v>
       </c>
       <c r="H16" s="3">
         <f>F16-G16</f>
@@ -49250,7 +49250,7 @@
         <v>193095220</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>103910327.142</v>
+        <v>103814434.342</v>
       </c>
       <c r="H17" s="3">
         <f>F17-G17</f>
